--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-allergyintolerance.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/AllergyIntolerance</t>
+    <t>http://hl7.org/fhir/StructureDefinition/AllergyIntolerance|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -366,7 +366,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -672,7 +672,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_AllergyIntolerance_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_AllergyIntolerance_VS|2023.9.25</t>
   </si>
   <si>
     <t>substance/product:@@ -701,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -724,7 +724,7 @@
     <t>AllergyIntolerance.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -790,7 +790,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -814,7 +814,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -955,7 +955,7 @@
     <t>物質のタイプを定義するコード（医薬品を含む）。 / Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+    <t>http://hl7.org/fhir/ValueSet/substance-code|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -981,7 +981,7 @@
     <t>有害反応イベントに観察または関連する臨床症状および/または徴候。 / Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1055,7 +1055,7 @@
     <t>被験者の体への、またはそれへの治療剤の投与の経路または生理学的経路を説明するコード化された概念。 / A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].routeCode</t>
@@ -1388,7 +1388,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="187.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1403,7 +1403,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="153.4765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.87109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-allergyintolerance.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/AllergyIntolerance|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/AllergyIntolerance</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -366,7 +366,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -672,7 +672,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_AllergyIntolerance_VS|2023.9.25</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_AllergyIntolerance_VS</t>
   </si>
   <si>
     <t>substance/product:@@ -701,7 +701,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -724,7 +724,7 @@
     <t>AllergyIntolerance.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -790,7 +790,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -814,7 +814,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole)
 </t>
   </si>
   <si>
@@ -955,7 +955,7 @@
     <t>物質のタイプを定義するコード（医薬品を含む）。 / Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/substance-code</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -981,7 +981,7 @@
     <t>有害反応イベントに観察または関連する臨床症状および/または徴候。 / Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1055,7 +1055,7 @@
     <t>被験者の体への、またはそれへの治療剤の投与の経路または生理学的経路を説明するコード化された概念。 / A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].routeCode</t>
@@ -1388,7 +1388,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="187.28515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1403,7 +1403,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="153.4765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.87109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
